--- a/data/vagary.xlsx
+++ b/data/vagary.xlsx
@@ -1,31 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Files\词频统计-Vagary\260720remake\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1F9990-2507-4351-897C-89D6720C1821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{056A3459-6725-4517-B829-A4909D06A8ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4245" yWindow="2010" windowWidth="21600" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$A$132</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="490">
   <si>
     <t>歌曲名</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -6756,6 +6768,84 @@
 点滴伤口见证成熟 痛楚只当祝福
 再来
 谢青春也曾留步 谢你我未曾踟躇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>归去来</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>易言</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>风露绽放青苔上的幽芳
+谷雨流连向重阳
+引我于春潮中游漾簪一枝梨棠
+亭台桥架鹊鸟忙忙
+星月悄渡云海汤汤
+一句莫失莫忘雷音响彻大荒
+万籁重生而你自何方登场
+人烟浩荡谁与我共炎凉四时心相撞
+隔世蓝桥下望或有恋恋金鳞凝眸过你脸庞
+杨柳岸已路过千百趟也曾邀晓风残月醉几抹残阳
+朦胧里相扶将
+小雪行尽云霓后再流浪
+吻落微寒的晴霜
+将白头山水盛一觞酿清明雨上
+蜉蝣轻衫映满暮光
+蝉鸣唤醒花泥暗香
+一声别来无恙铃虫趁夜低唱
+问我如何不识它今宵模样
+人烟浩荡谁与我共炎凉四时心相撞
+隔世蓝桥下望或有恋恋金鳞凝眸过你脸庞
+杨柳岸已路过千百趟也曾邀晓风残月醉几抹残阳
+朦胧里相扶将
+尘寰浩荡你与我两相望溅石火电光
+最后默然擦肩只剩似曾相识刹那往心尖烫
+是前生衔去我鬓边香或彼岸生根在你必经的路旁
+攒相约一万场
+归去来不相忘</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>琉璃契</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>文森</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是那天机天命 斩不断的契
+是你惹出的泪光 烫醒这心意
+恼海风吹砂入隙 不肯解语
+原来是我 还未曾 遇着你
+生来此身太混沌 逞孤勇 斗顽狠
+懂甚隐忍 迎不平 便生嗔
+而你白衣清冽 含笑叩我心门
+这一见留痕 风波结赤忱 最是少年人
+暮色里比肩长坐 涛声中无语也真
+你我身后 皆坎坷红尘
+管什么天劫孤辰 甲胄在身
+并肩折碎九霄风雷刃
+共你将命途重写 再整乾坤
+Music.
+烈烈枪风吹不舍 你问我 是为何
+成佛成魔 怎丢得 这澄澈
+愿我做你心中 最无瑕那一个
+这一见难分 白雪温烈火 红莲暖冰魂
+焚不绝千年旧梦 冻不灭热血前尘
+亘古温存 揉成一双人
+怕什么海狱幽深 升仙无门
+天地又能缚你我几分？
+从此后悲欢共品 苦乐共斟
+这一见难分 琉璃经孽焰 剔透藏温存
+我偏要正邪同道 如你我冰火同樽
+倾世豪饮 醉倒了青春
+理什么地厚天高 森列星辰
+万古混元何惧烽烟深
+从此后执手同行 永不离分</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -7095,17 +7185,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I131"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I133"/>
+  <sheetFormatPr defaultRowHeight="14.15" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.375" customWidth="1"/>
-    <col min="2" max="2" width="18.25" customWidth="1"/>
-    <col min="3" max="3" width="11.75" customWidth="1"/>
-    <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="6" max="6" width="16.625" customWidth="1"/>
+    <col min="1" max="1" width="17.35546875" customWidth="1"/>
+    <col min="2" max="2" width="18.2109375" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7134,7 +7224,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>30</v>
       </c>
@@ -7163,7 +7253,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -7183,7 +7273,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -7203,7 +7293,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -7223,7 +7313,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>49</v>
       </c>
@@ -7246,7 +7336,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -7266,7 +7356,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>56</v>
       </c>
@@ -7286,7 +7376,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>62</v>
       </c>
@@ -7312,7 +7402,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>481</v>
       </c>
@@ -7328,11 +7418,11 @@
       <c r="E10" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>66</v>
       </c>
@@ -7355,7 +7445,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -7375,7 +7465,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -7395,7 +7485,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -7418,7 +7508,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>83</v>
       </c>
@@ -7438,7 +7528,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>6</v>
       </c>
@@ -7464,7 +7554,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -7487,7 +7577,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>90</v>
       </c>
@@ -7510,7 +7600,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>97</v>
       </c>
@@ -7530,7 +7620,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>99</v>
       </c>
@@ -7550,7 +7640,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>101</v>
       </c>
@@ -7573,7 +7663,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>106</v>
       </c>
@@ -7596,7 +7686,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>110</v>
       </c>
@@ -7616,7 +7706,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>115</v>
       </c>
@@ -7636,7 +7726,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>119</v>
       </c>
@@ -7656,7 +7746,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>122</v>
       </c>
@@ -7676,7 +7766,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>124</v>
       </c>
@@ -7696,7 +7786,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>127</v>
       </c>
@@ -7716,7 +7806,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>134</v>
       </c>
@@ -7736,7 +7826,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -7756,7 +7846,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>136</v>
       </c>
@@ -7776,7 +7866,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>139</v>
       </c>
@@ -7799,7 +7889,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>143</v>
       </c>
@@ -7822,7 +7912,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>146</v>
       </c>
@@ -7842,7 +7932,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>150</v>
       </c>
@@ -7862,7 +7952,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>156</v>
       </c>
@@ -7882,7 +7972,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>157</v>
       </c>
@@ -7902,7 +7992,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>161</v>
       </c>
@@ -7922,7 +8012,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>173</v>
       </c>
@@ -7942,7 +8032,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>174</v>
       </c>
@@ -7962,7 +8052,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>175</v>
       </c>
@@ -7982,7 +8072,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>179</v>
       </c>
@@ -8005,7 +8095,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>183</v>
       </c>
@@ -8025,7 +8115,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>187</v>
       </c>
@@ -8045,924 +8135,921 @@
         <v>190</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>484</v>
+      </c>
+      <c r="B45" t="s">
+        <v>485</v>
+      </c>
+      <c r="C45" t="s">
+        <v>152</v>
+      </c>
+      <c r="D45" t="s">
+        <v>153</v>
+      </c>
+      <c r="E45" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>191</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>22</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C46" t="s">
         <v>14</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D46" t="s">
         <v>14</v>
       </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="E46" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>193</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>194</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>195</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>196</v>
       </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="E47" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>198</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>199</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>200</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" t="s">
         <v>202</v>
       </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
+      <c r="E48" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+    <row r="49" spans="1:6" ht="17.149999999999999" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
         <v>203</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" t="s">
         <v>204</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>205</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>206</v>
       </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
+      <c r="E49" t="s">
+        <v>7</v>
+      </c>
+      <c r="F49" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>208</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B50" t="s">
         <v>78</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C50" t="s">
         <v>164</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D50" t="s">
         <v>209</v>
       </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="E50" t="s">
+        <v>7</v>
+      </c>
+      <c r="F50" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A50" t="s">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>211</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B51" t="s">
         <v>212</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C51" t="s">
         <v>148</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D51" t="s">
         <v>148</v>
       </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="E51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F51" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>214</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B52" t="s">
         <v>26</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C52" t="s">
         <v>26</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D52" t="s">
         <v>93</v>
       </c>
-      <c r="E51" t="s">
-        <v>7</v>
-      </c>
-      <c r="F51" t="s">
+      <c r="E52" t="s">
+        <v>7</v>
+      </c>
+      <c r="F52" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>216</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B53" t="s">
         <v>217</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C53" t="s">
         <v>218</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D53" t="s">
         <v>218</v>
       </c>
-      <c r="E52" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="E53" t="s">
+        <v>7</v>
+      </c>
+      <c r="F53" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>220</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B54" t="s">
         <v>221</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C54" t="s">
         <v>222</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D54" t="s">
         <v>223</v>
       </c>
-      <c r="E53" t="s">
-        <v>7</v>
-      </c>
-      <c r="F53" t="s">
+      <c r="E54" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>225</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B55" t="s">
         <v>226</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C55" t="s">
         <v>116</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D55" t="s">
         <v>112</v>
       </c>
-      <c r="E54" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="E55" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>228</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B56" t="s">
         <v>45</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C56" t="s">
         <v>53</v>
       </c>
-      <c r="D55" t="s">
+      <c r="D56" t="s">
         <v>53</v>
       </c>
-      <c r="E55" t="s">
-        <v>7</v>
-      </c>
-      <c r="F55" t="s">
+      <c r="E56" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>230</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B57" t="s">
         <v>128</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C57" t="s">
         <v>231</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D57" t="s">
         <v>232</v>
       </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" t="s">
+      <c r="E57" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>234</v>
       </c>
-      <c r="B57" t="s">
+      <c r="B58" t="s">
         <v>152</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C58" t="s">
         <v>235</v>
       </c>
-      <c r="D57" t="s">
+      <c r="D58" t="s">
         <v>236</v>
       </c>
-      <c r="E57" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="E58" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>238</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B59" t="s">
         <v>239</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C59" t="s">
         <v>14</v>
       </c>
-      <c r="D58" t="s">
+      <c r="D59" t="s">
         <v>14</v>
       </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
+      <c r="E59" t="s">
+        <v>7</v>
+      </c>
+      <c r="F59" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>241</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B60" t="s">
         <v>242</v>
-      </c>
-      <c r="C59" t="s">
-        <v>116</v>
-      </c>
-      <c r="D59" t="s">
-        <v>37</v>
-      </c>
-      <c r="E59" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>245</v>
-      </c>
-      <c r="B60" t="s">
-        <v>244</v>
       </c>
       <c r="C60" t="s">
         <v>116</v>
       </c>
       <c r="D60" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>245</v>
+      </c>
+      <c r="B61" t="s">
+        <v>244</v>
+      </c>
+      <c r="C61" t="s">
+        <v>116</v>
+      </c>
+      <c r="D61" t="s">
         <v>120</v>
       </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" t="s">
+      <c r="E61" t="s">
+        <v>7</v>
+      </c>
+      <c r="F61" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>247</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B62" t="s">
         <v>248</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C62" t="s">
         <v>250</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D62" t="s">
         <v>250</v>
       </c>
-      <c r="E61" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" t="s">
+      <c r="E62" t="s">
+        <v>7</v>
+      </c>
+      <c r="F62" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>487</v>
+      </c>
+      <c r="B63" t="s">
+        <v>488</v>
+      </c>
+      <c r="C63" t="s">
+        <v>235</v>
+      </c>
+      <c r="D63" t="s">
+        <v>235</v>
+      </c>
+      <c r="E63" t="s">
+        <v>7</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>251</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B64" t="s">
         <v>252</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C64" t="s">
         <v>253</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D64" t="s">
         <v>254</v>
       </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
+      <c r="E64" t="s">
+        <v>7</v>
+      </c>
+      <c r="F64" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>471</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B65" t="s">
         <v>188</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C65" t="s">
         <v>14</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D65" t="s">
         <v>14</v>
       </c>
-      <c r="E63" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" t="s">
+      <c r="E65" t="s">
+        <v>7</v>
+      </c>
+      <c r="F65" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
         <v>256</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B66" t="s">
         <v>257</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C66" t="s">
         <v>258</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D66" t="s">
         <v>258</v>
       </c>
-      <c r="E64" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" t="s">
+      <c r="E66" t="s">
+        <v>7</v>
+      </c>
+      <c r="F66" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
         <v>260</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B67" t="s">
         <v>261</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C67" t="s">
         <v>261</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D67" t="s">
         <v>159</v>
       </c>
-      <c r="E65" t="s">
-        <v>7</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="E67" t="s">
+        <v>7</v>
+      </c>
+      <c r="F67" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
         <v>263</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B68" t="s">
         <v>152</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C68" t="s">
         <v>152</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D68" t="s">
         <v>265</v>
       </c>
-      <c r="E66" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" t="s">
+      <c r="E68" t="s">
+        <v>7</v>
+      </c>
+      <c r="F68" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
         <v>266</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B69" t="s">
         <v>78</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C69" t="s">
         <v>79</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D69" t="s">
         <v>79</v>
       </c>
-      <c r="E67" t="s">
-        <v>7</v>
-      </c>
-      <c r="F67" t="s">
+      <c r="E69" t="s">
+        <v>7</v>
+      </c>
+      <c r="F69" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
         <v>268</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B70" t="s">
         <v>269</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C70" t="s">
         <v>270</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D70" t="s">
         <v>270</v>
       </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
+      <c r="E70" t="s">
+        <v>7</v>
+      </c>
+      <c r="F70" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>272</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B71" t="s">
         <v>273</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C71" t="s">
         <v>77</v>
       </c>
-      <c r="D69" t="s">
+      <c r="D71" t="s">
         <v>93</v>
       </c>
-      <c r="E69" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69" t="s">
+      <c r="E71" t="s">
+        <v>7</v>
+      </c>
+      <c r="F71" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
         <v>275</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B72" t="s">
         <v>168</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C72" t="s">
         <v>276</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D72" t="s">
         <v>85</v>
       </c>
-      <c r="E70" t="s">
-        <v>7</v>
-      </c>
-      <c r="F70" t="s">
+      <c r="E72" t="s">
+        <v>7</v>
+      </c>
+      <c r="F72" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
         <v>278</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B73" t="s">
         <v>78</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C73" t="s">
         <v>166</v>
       </c>
-      <c r="D71" t="s">
+      <c r="D73" t="s">
         <v>166</v>
       </c>
-      <c r="E71" t="s">
-        <v>7</v>
-      </c>
-      <c r="F71" t="s">
+      <c r="E73" t="s">
+        <v>7</v>
+      </c>
+      <c r="F73" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
         <v>280</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B74" t="s">
         <v>281</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C74" t="s">
         <v>26</v>
       </c>
-      <c r="D72" t="s">
+      <c r="D74" t="s">
         <v>93</v>
       </c>
-      <c r="E72" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" t="s">
+      <c r="E74" t="s">
+        <v>7</v>
+      </c>
+      <c r="F74" t="s">
         <v>283</v>
       </c>
-      <c r="G72" t="s">
+      <c r="G74" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
         <v>285</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B75" t="s">
         <v>284</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C75" t="s">
         <v>286</v>
       </c>
-      <c r="D73" t="s">
+      <c r="D75" t="s">
         <v>287</v>
       </c>
-      <c r="E73" t="s">
-        <v>7</v>
-      </c>
-      <c r="F73" t="s">
+      <c r="E75" t="s">
+        <v>7</v>
+      </c>
+      <c r="F75" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>289</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B76" t="s">
         <v>286</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C76" t="s">
         <v>286</v>
       </c>
-      <c r="D74" t="s">
+      <c r="D76" t="s">
         <v>290</v>
       </c>
-      <c r="E74" t="s">
-        <v>7</v>
-      </c>
-      <c r="F74" t="s">
+      <c r="E76" t="s">
+        <v>7</v>
+      </c>
+      <c r="F76" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>292</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B77" t="s">
         <v>78</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C77" t="s">
         <v>166</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D77" t="s">
         <v>166</v>
       </c>
-      <c r="E75" t="s">
-        <v>7</v>
-      </c>
-      <c r="F75" t="s">
+      <c r="E77" t="s">
+        <v>7</v>
+      </c>
+      <c r="F77" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A76" t="s">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>294</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B78" t="s">
         <v>295</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C78" t="s">
         <v>254</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D78" t="s">
         <v>254</v>
       </c>
-      <c r="E76" t="s">
-        <v>7</v>
-      </c>
-      <c r="F76" t="s">
+      <c r="E78" t="s">
+        <v>7</v>
+      </c>
+      <c r="F78" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A77" t="s">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>297</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B79" t="s">
         <v>299</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C79" t="s">
         <v>14</v>
       </c>
-      <c r="D77" t="s">
+      <c r="D79" t="s">
         <v>14</v>
       </c>
-      <c r="E77" t="s">
-        <v>7</v>
-      </c>
-      <c r="F77" t="s">
+      <c r="E79" t="s">
+        <v>7</v>
+      </c>
+      <c r="F79" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A78" t="s">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>300</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B80" t="s">
         <v>301</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C80" t="s">
         <v>302</v>
       </c>
-      <c r="D78" t="s">
+      <c r="D80" t="s">
         <v>302</v>
       </c>
-      <c r="E78" t="s">
-        <v>7</v>
-      </c>
-      <c r="F78" t="s">
+      <c r="E80" t="s">
+        <v>7</v>
+      </c>
+      <c r="F80" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A79" t="s">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>304</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B81" t="s">
         <v>305</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C81" t="s">
         <v>306</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D81" t="s">
         <v>307</v>
       </c>
-      <c r="E79" t="s">
-        <v>7</v>
-      </c>
-      <c r="F79" t="s">
+      <c r="E81" t="s">
+        <v>7</v>
+      </c>
+      <c r="F81" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80" t="s">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>309</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B82" t="s">
         <v>310</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C82" t="s">
         <v>53</v>
       </c>
-      <c r="D80" t="s">
+      <c r="D82" t="s">
         <v>53</v>
       </c>
-      <c r="E80" t="s">
-        <v>7</v>
-      </c>
-      <c r="F80" t="s">
+      <c r="E82" t="s">
+        <v>7</v>
+      </c>
+      <c r="F82" t="s">
         <v>312</v>
       </c>
-      <c r="G80" t="s">
+      <c r="G82" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A81" t="s">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>313</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B83" t="s">
         <v>78</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C83" t="s">
         <v>166</v>
       </c>
-      <c r="D81" t="s">
+      <c r="D83" t="s">
         <v>166</v>
       </c>
-      <c r="E81" t="s">
-        <v>7</v>
-      </c>
-      <c r="F81" t="s">
+      <c r="E83" t="s">
+        <v>7</v>
+      </c>
+      <c r="F83" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A82" t="s">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>317</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B84" t="s">
         <v>316</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C84" t="s">
         <v>318</v>
       </c>
-      <c r="D82" t="s">
+      <c r="D84" t="s">
         <v>318</v>
       </c>
-      <c r="E82" t="s">
-        <v>7</v>
-      </c>
-      <c r="F82" t="s">
+      <c r="E84" t="s">
+        <v>7</v>
+      </c>
+      <c r="F84" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A83" t="s">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>467</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B85" t="s">
         <v>468</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C85" t="s">
         <v>469</v>
       </c>
-      <c r="D83" t="s">
+      <c r="D85" t="s">
         <v>14</v>
       </c>
-      <c r="E83" t="s">
-        <v>7</v>
-      </c>
-      <c r="F83" t="s">
+      <c r="E85" t="s">
+        <v>7</v>
+      </c>
+      <c r="F85" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A84" t="s">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>320</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B86" t="s">
         <v>322</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C86" t="s">
         <v>321</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D86" t="s">
         <v>321</v>
       </c>
-      <c r="E84" t="s">
-        <v>7</v>
-      </c>
-      <c r="F84" t="s">
+      <c r="E86" t="s">
+        <v>7</v>
+      </c>
+      <c r="F86" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A85" t="s">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>324</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B87" t="s">
         <v>78</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C87" t="s">
         <v>166</v>
       </c>
-      <c r="D85" t="s">
+      <c r="D87" t="s">
         <v>166</v>
       </c>
-      <c r="E85" t="s">
-        <v>7</v>
-      </c>
-      <c r="F85" t="s">
+      <c r="E87" t="s">
+        <v>7</v>
+      </c>
+      <c r="F87" t="s">
         <v>326</v>
       </c>
-      <c r="G85" t="s">
+      <c r="G87" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A86" t="s">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
         <v>476</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B88" t="s">
         <v>477</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C88" t="s">
         <v>254</v>
       </c>
-      <c r="D86" t="s">
+      <c r="D88" t="s">
         <v>254</v>
       </c>
-      <c r="E86" t="s">
-        <v>7</v>
-      </c>
-      <c r="F86" t="s">
+      <c r="E88" t="s">
+        <v>7</v>
+      </c>
+      <c r="F88" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A87" t="s">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>327</v>
-      </c>
-      <c r="B87" t="s">
-        <v>159</v>
-      </c>
-      <c r="C87" t="s">
-        <v>159</v>
-      </c>
-      <c r="D87" t="s">
-        <v>159</v>
-      </c>
-      <c r="E87" t="s">
-        <v>7</v>
-      </c>
-      <c r="F87" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A88" t="s">
-        <v>329</v>
-      </c>
-      <c r="B88" t="s">
-        <v>78</v>
-      </c>
-      <c r="C88" t="s">
-        <v>166</v>
-      </c>
-      <c r="D88" t="s">
-        <v>166</v>
-      </c>
-      <c r="E88" t="s">
-        <v>7</v>
-      </c>
-      <c r="F88" t="s">
-        <v>330</v>
-      </c>
-      <c r="H88" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A89" t="s">
-        <v>332</v>
       </c>
       <c r="B89" t="s">
         <v>159</v>
       </c>
       <c r="C89" t="s">
-        <v>333</v>
+        <v>159</v>
       </c>
       <c r="D89" t="s">
-        <v>120</v>
+        <v>159</v>
       </c>
       <c r="E89" t="s">
         <v>7</v>
       </c>
       <c r="F89" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="B90" t="s">
-        <v>335</v>
+        <v>78</v>
       </c>
       <c r="C90" t="s">
         <v>166</v>
@@ -8974,850 +9061,894 @@
         <v>7</v>
       </c>
       <c r="F90" t="s">
+        <v>330</v>
+      </c>
+      <c r="H90" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>332</v>
+      </c>
+      <c r="B91" t="s">
+        <v>159</v>
+      </c>
+      <c r="C91" t="s">
+        <v>333</v>
+      </c>
+      <c r="D91" t="s">
+        <v>120</v>
+      </c>
+      <c r="E91" t="s">
+        <v>7</v>
+      </c>
+      <c r="F91" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>334</v>
+      </c>
+      <c r="B92" t="s">
+        <v>335</v>
+      </c>
+      <c r="C92" t="s">
+        <v>166</v>
+      </c>
+      <c r="D92" t="s">
+        <v>166</v>
+      </c>
+      <c r="E92" t="s">
+        <v>7</v>
+      </c>
+      <c r="F92" t="s">
         <v>337</v>
       </c>
-      <c r="G90" t="s">
+      <c r="G92" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A91" t="s">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
         <v>338</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B93" t="s">
         <v>339</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C93" t="s">
         <v>340</v>
       </c>
-      <c r="D91" t="s">
+      <c r="D93" t="s">
         <v>340</v>
       </c>
-      <c r="E91" t="s">
-        <v>7</v>
-      </c>
-      <c r="F91" t="s">
+      <c r="E93" t="s">
+        <v>7</v>
+      </c>
+      <c r="F93" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A92" t="s">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>342</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B94" t="s">
         <v>343</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C94" t="s">
         <v>14</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D94" t="s">
         <v>14</v>
       </c>
-      <c r="E92" t="s">
-        <v>7</v>
-      </c>
-      <c r="F92" t="s">
+      <c r="E94" t="s">
+        <v>7</v>
+      </c>
+      <c r="F94" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A93" t="s">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
         <v>346</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B95" t="s">
         <v>345</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C95" t="s">
         <v>347</v>
       </c>
-      <c r="D93" t="s">
+      <c r="D95" t="s">
         <v>347</v>
       </c>
-      <c r="E93" t="s">
-        <v>7</v>
-      </c>
-      <c r="F93" t="s">
+      <c r="E95" t="s">
+        <v>7</v>
+      </c>
+      <c r="F95" t="s">
         <v>348</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A94" t="s">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
         <v>349</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B96" t="s">
         <v>248</v>
-      </c>
-      <c r="C94" t="s">
-        <v>314</v>
-      </c>
-      <c r="D94" t="s">
-        <v>166</v>
-      </c>
-      <c r="E94" t="s">
-        <v>7</v>
-      </c>
-      <c r="F94" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A95" t="s">
-        <v>351</v>
-      </c>
-      <c r="B95" t="s">
-        <v>78</v>
-      </c>
-      <c r="C95" t="s">
-        <v>78</v>
-      </c>
-      <c r="D95" t="s">
-        <v>166</v>
-      </c>
-      <c r="E95" t="s">
-        <v>7</v>
-      </c>
-      <c r="F95" t="s">
-        <v>353</v>
-      </c>
-      <c r="G95" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A96" t="s">
-        <v>354</v>
-      </c>
-      <c r="B96" t="s">
-        <v>78</v>
       </c>
       <c r="C96" t="s">
         <v>314</v>
       </c>
       <c r="D96" t="s">
+        <v>166</v>
+      </c>
+      <c r="E96" t="s">
+        <v>7</v>
+      </c>
+      <c r="F96" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>351</v>
+      </c>
+      <c r="B97" t="s">
+        <v>78</v>
+      </c>
+      <c r="C97" t="s">
+        <v>78</v>
+      </c>
+      <c r="D97" t="s">
+        <v>166</v>
+      </c>
+      <c r="E97" t="s">
+        <v>7</v>
+      </c>
+      <c r="F97" t="s">
+        <v>353</v>
+      </c>
+      <c r="G97" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>354</v>
+      </c>
+      <c r="B98" t="s">
+        <v>78</v>
+      </c>
+      <c r="C98" t="s">
         <v>314</v>
       </c>
-      <c r="E96" t="s">
-        <v>7</v>
-      </c>
-      <c r="F96" t="s">
+      <c r="D98" t="s">
+        <v>314</v>
+      </c>
+      <c r="E98" t="s">
+        <v>7</v>
+      </c>
+      <c r="F98" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A97" t="s">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
         <v>356</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B99" t="s">
         <v>13</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C99" t="s">
         <v>98</v>
       </c>
-      <c r="D97" t="s">
+      <c r="D99" t="s">
         <v>98</v>
       </c>
-      <c r="E97" t="s">
-        <v>7</v>
-      </c>
-      <c r="F97" t="s">
+      <c r="E99" t="s">
+        <v>7</v>
+      </c>
+      <c r="F99" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
         <v>358</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B100" t="s">
         <v>359</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C100" t="s">
         <v>86</v>
       </c>
-      <c r="D98" t="s">
+      <c r="D100" t="s">
         <v>360</v>
       </c>
-      <c r="E98" t="s">
-        <v>7</v>
-      </c>
-      <c r="F98" t="s">
+      <c r="E100" t="s">
+        <v>7</v>
+      </c>
+      <c r="F100" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99" t="s">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
         <v>362</v>
       </c>
-      <c r="B99" t="s">
+      <c r="B101" t="s">
         <v>364</v>
       </c>
-      <c r="C99" t="s">
+      <c r="C101" t="s">
         <v>363</v>
       </c>
-      <c r="D99" t="s">
+      <c r="D101" t="s">
         <v>363</v>
       </c>
-      <c r="E99" t="s">
-        <v>7</v>
-      </c>
-      <c r="F99" t="s">
+      <c r="E101" t="s">
+        <v>7</v>
+      </c>
+      <c r="F101" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A100" t="s">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
         <v>366</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B102" t="s">
         <v>368</v>
       </c>
-      <c r="C100" t="s">
+      <c r="C102" t="s">
         <v>221</v>
       </c>
-      <c r="D100" t="s">
+      <c r="D102" t="s">
         <v>276</v>
       </c>
-      <c r="E100" t="s">
-        <v>7</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="E102" t="s">
+        <v>7</v>
+      </c>
+      <c r="F102" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A101" t="s">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
         <v>16</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B103" t="s">
         <v>17</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C103" t="s">
         <v>18</v>
       </c>
-      <c r="D101" t="s">
+      <c r="D103" t="s">
         <v>19</v>
       </c>
-      <c r="E101" t="s">
-        <v>7</v>
-      </c>
-      <c r="F101" t="s">
+      <c r="E103" t="s">
+        <v>7</v>
+      </c>
+      <c r="F103" t="s">
         <v>20</v>
       </c>
-      <c r="G101" t="s">
+      <c r="G103" t="s">
         <v>15</v>
       </c>
-      <c r="H101" t="s">
+      <c r="H103" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A102" t="s">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
         <v>370</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B104" t="s">
         <v>369</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C104" t="s">
         <v>371</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D104" t="s">
         <v>372</v>
       </c>
-      <c r="E102" t="s">
-        <v>7</v>
-      </c>
-      <c r="F102" t="s">
+      <c r="E104" t="s">
+        <v>7</v>
+      </c>
+      <c r="F104" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A103" t="s">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
         <v>374</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B105" t="s">
         <v>375</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C105" t="s">
         <v>116</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D105" t="s">
         <v>120</v>
       </c>
-      <c r="E103" t="s">
-        <v>7</v>
-      </c>
-      <c r="F103" t="s">
+      <c r="E105" t="s">
+        <v>7</v>
+      </c>
+      <c r="F105" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
         <v>377</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B106" t="s">
         <v>378</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C106" t="s">
         <v>14</v>
       </c>
-      <c r="D104" t="s">
+      <c r="D106" t="s">
         <v>14</v>
       </c>
-      <c r="E104" t="s">
-        <v>7</v>
-      </c>
-      <c r="F104" t="s">
+      <c r="E106" t="s">
+        <v>7</v>
+      </c>
+      <c r="F106" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A105" t="s">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
         <v>380</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B107" t="s">
         <v>381</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C107" t="s">
         <v>235</v>
       </c>
-      <c r="D105" t="s">
+      <c r="D107" t="s">
         <v>382</v>
       </c>
-      <c r="E105" t="s">
-        <v>7</v>
-      </c>
-      <c r="F105" t="s">
+      <c r="E107" t="s">
+        <v>7</v>
+      </c>
+      <c r="F107" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A106" t="s">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
         <v>384</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B108" t="s">
         <v>385</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C108" t="s">
         <v>74</v>
       </c>
-      <c r="D106" t="s">
+      <c r="D108" t="s">
         <v>74</v>
       </c>
-      <c r="E106" t="s">
-        <v>7</v>
-      </c>
-      <c r="F106" t="s">
+      <c r="E108" t="s">
+        <v>7</v>
+      </c>
+      <c r="F108" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A107" t="s">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
         <v>387</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B109" t="s">
         <v>388</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C109" t="s">
         <v>314</v>
       </c>
-      <c r="D107" t="s">
+      <c r="D109" t="s">
         <v>314</v>
       </c>
-      <c r="E107" t="s">
-        <v>7</v>
-      </c>
-      <c r="F107" t="s">
+      <c r="E109" t="s">
+        <v>7</v>
+      </c>
+      <c r="F109" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
         <v>390</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B110" t="s">
         <v>391</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C110" t="s">
         <v>26</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D110" t="s">
         <v>93</v>
       </c>
-      <c r="E108" t="s">
-        <v>7</v>
-      </c>
-      <c r="F108" t="s">
+      <c r="E110" t="s">
+        <v>7</v>
+      </c>
+      <c r="F110" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
         <v>393</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B111" t="s">
         <v>394</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C111" t="s">
         <v>306</v>
       </c>
-      <c r="D109" t="s">
+      <c r="D111" t="s">
         <v>104</v>
       </c>
-      <c r="E109" t="s">
-        <v>7</v>
-      </c>
-      <c r="F109" t="s">
+      <c r="E111" t="s">
+        <v>7</v>
+      </c>
+      <c r="F111" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
         <v>396</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B112" t="s">
         <v>397</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C112" t="s">
         <v>399</v>
       </c>
-      <c r="D110" t="s">
+      <c r="D112" t="s">
         <v>185</v>
       </c>
-      <c r="E110" t="s">
-        <v>7</v>
-      </c>
-      <c r="F110" t="s">
+      <c r="E112" t="s">
+        <v>7</v>
+      </c>
+      <c r="F112" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
         <v>401</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B113" t="s">
         <v>400</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C113" t="s">
         <v>14</v>
       </c>
-      <c r="D111" t="s">
+      <c r="D113" t="s">
         <v>402</v>
       </c>
-      <c r="E111" t="s">
-        <v>7</v>
-      </c>
-      <c r="F111" t="s">
+      <c r="E113" t="s">
+        <v>7</v>
+      </c>
+      <c r="F113" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
         <v>404</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B114" t="s">
         <v>405</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C114" t="s">
         <v>318</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D114" t="s">
         <v>318</v>
       </c>
-      <c r="E112" t="s">
-        <v>7</v>
-      </c>
-      <c r="F112" t="s">
+      <c r="E114" t="s">
+        <v>7</v>
+      </c>
+      <c r="F114" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
         <v>407</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B115" t="s">
         <v>408</v>
       </c>
-      <c r="C113" t="s">
+      <c r="C115" t="s">
         <v>409</v>
       </c>
-      <c r="D113" t="s">
+      <c r="D115" t="s">
         <v>410</v>
       </c>
-      <c r="E113" t="s">
-        <v>7</v>
-      </c>
-      <c r="F113" t="s">
+      <c r="E115" t="s">
+        <v>7</v>
+      </c>
+      <c r="F115" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
         <v>412</v>
       </c>
-      <c r="B114" t="s">
+      <c r="B116" t="s">
         <v>413</v>
       </c>
-      <c r="C114" t="s">
+      <c r="C116" t="s">
         <v>414</v>
       </c>
-      <c r="D114" t="s">
+      <c r="D116" t="s">
         <v>414</v>
       </c>
-      <c r="E114" t="s">
-        <v>7</v>
-      </c>
-      <c r="F114" t="s">
+      <c r="E116" t="s">
+        <v>7</v>
+      </c>
+      <c r="F116" t="s">
         <v>415</v>
       </c>
-      <c r="G114" t="s">
+      <c r="G116" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
         <v>417</v>
       </c>
-      <c r="B115" t="s">
+      <c r="B117" t="s">
         <v>78</v>
       </c>
-      <c r="C115" t="s">
+      <c r="C117" t="s">
         <v>180</v>
       </c>
-      <c r="D115" t="s">
+      <c r="D117" t="s">
         <v>180</v>
       </c>
-      <c r="E115" t="s">
-        <v>7</v>
-      </c>
-      <c r="F115" t="s">
+      <c r="E117" t="s">
+        <v>7</v>
+      </c>
+      <c r="F117" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
         <v>419</v>
       </c>
-      <c r="B116" t="s">
+      <c r="B118" t="s">
         <v>420</v>
       </c>
-      <c r="C116" t="s">
+      <c r="C118" t="s">
         <v>258</v>
       </c>
-      <c r="D116" t="s">
+      <c r="D118" t="s">
         <v>258</v>
       </c>
-      <c r="E116" t="s">
-        <v>7</v>
-      </c>
-      <c r="F116" t="s">
+      <c r="E118" t="s">
+        <v>7</v>
+      </c>
+      <c r="F118" t="s">
         <v>422</v>
       </c>
-      <c r="G116" t="s">
+      <c r="G118" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
         <v>423</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B119" t="s">
         <v>424</v>
       </c>
-      <c r="C117" t="s">
+      <c r="C119" t="s">
         <v>425</v>
       </c>
-      <c r="D117" t="s">
+      <c r="D119" t="s">
         <v>425</v>
       </c>
-      <c r="E117" t="s">
-        <v>7</v>
-      </c>
-      <c r="F117" t="s">
+      <c r="E119" t="s">
+        <v>7</v>
+      </c>
+      <c r="F119" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
         <v>427</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B120" t="s">
         <v>428</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C120" t="s">
         <v>429</v>
       </c>
-      <c r="D118" t="s">
+      <c r="D120" t="s">
         <v>429</v>
       </c>
-      <c r="E118" t="s">
-        <v>7</v>
-      </c>
-      <c r="F118" t="s">
+      <c r="E120" t="s">
+        <v>7</v>
+      </c>
+      <c r="F120" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
         <v>431</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B121" t="s">
         <v>212</v>
       </c>
-      <c r="C119" t="s">
+      <c r="C121" t="s">
         <v>302</v>
       </c>
-      <c r="D119" t="s">
+      <c r="D121" t="s">
         <v>302</v>
       </c>
-      <c r="E119" t="s">
-        <v>7</v>
-      </c>
-      <c r="F119" t="s">
+      <c r="E121" t="s">
+        <v>7</v>
+      </c>
+      <c r="F121" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
         <v>433</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B122" t="s">
         <v>420</v>
       </c>
-      <c r="C120" t="s">
+      <c r="C122" t="s">
         <v>14</v>
       </c>
-      <c r="D120" t="s">
+      <c r="D122" t="s">
         <v>14</v>
       </c>
-      <c r="E120" t="s">
-        <v>7</v>
-      </c>
-      <c r="F120" t="s">
+      <c r="E122" t="s">
+        <v>7</v>
+      </c>
+      <c r="F122" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A121" t="s">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A123" t="s">
         <v>436</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B123" t="s">
         <v>78</v>
       </c>
-      <c r="C121" t="s">
+      <c r="C123" t="s">
         <v>250</v>
       </c>
-      <c r="D121" t="s">
+      <c r="D123" t="s">
         <v>250</v>
       </c>
-      <c r="E121" t="s">
-        <v>7</v>
-      </c>
-      <c r="F121" t="s">
+      <c r="E123" t="s">
+        <v>7</v>
+      </c>
+      <c r="F123" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A122" t="s">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
         <v>438</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B124" t="s">
         <v>439</v>
       </c>
-      <c r="C122" t="s">
+      <c r="C124" t="s">
         <v>314</v>
       </c>
-      <c r="D122" t="s">
+      <c r="D124" t="s">
         <v>314</v>
       </c>
-      <c r="E122" t="s">
-        <v>7</v>
-      </c>
-      <c r="F122" t="s">
+      <c r="E124" t="s">
+        <v>7</v>
+      </c>
+      <c r="F124" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A123" t="s">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
         <v>473</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B125" t="s">
         <v>409</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C125" t="s">
         <v>474</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D125" t="s">
         <v>104</v>
       </c>
-      <c r="E123" t="s">
-        <v>7</v>
-      </c>
-      <c r="F123" t="s">
+      <c r="E125" t="s">
+        <v>7</v>
+      </c>
+      <c r="F125" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A124" t="s">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
         <v>442</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B126" t="s">
         <v>479</v>
       </c>
-      <c r="C124" t="s">
+      <c r="C126" t="s">
         <v>441</v>
       </c>
-      <c r="D124" t="s">
+      <c r="D126" t="s">
         <v>480</v>
       </c>
-      <c r="E124" t="s">
-        <v>7</v>
-      </c>
-      <c r="F124" t="s">
+      <c r="E126" t="s">
+        <v>7</v>
+      </c>
+      <c r="F126" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A125" t="s">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A127" t="s">
         <v>444</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B127" t="s">
         <v>445</v>
       </c>
-      <c r="C125" t="s">
+      <c r="C127" t="s">
         <v>446</v>
       </c>
-      <c r="D125" t="s">
+      <c r="D127" t="s">
         <v>446</v>
       </c>
-      <c r="E125" t="s">
-        <v>7</v>
-      </c>
-      <c r="F125" t="s">
+      <c r="E127" t="s">
+        <v>7</v>
+      </c>
+      <c r="F127" t="s">
         <v>447</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A126" t="s">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
         <v>448</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B128" t="s">
         <v>449</v>
       </c>
-      <c r="C126" t="s">
+      <c r="C128" t="s">
         <v>159</v>
       </c>
-      <c r="D126" t="s">
+      <c r="D128" t="s">
         <v>159</v>
       </c>
-      <c r="E126" t="s">
-        <v>7</v>
-      </c>
-      <c r="F126" t="s">
+      <c r="E128" t="s">
+        <v>7</v>
+      </c>
+      <c r="F128" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A127" t="s">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
         <v>451</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B129" t="s">
         <v>452</v>
       </c>
-      <c r="C127" t="s">
+      <c r="C129" t="s">
         <v>159</v>
       </c>
-      <c r="D127" t="s">
+      <c r="D129" t="s">
         <v>159</v>
       </c>
-      <c r="E127" t="s">
-        <v>7</v>
-      </c>
-      <c r="F127" t="s">
+      <c r="E129" t="s">
+        <v>7</v>
+      </c>
+      <c r="F129" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A128" t="s">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
         <v>454</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B130" t="s">
         <v>455</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C130" t="s">
         <v>176</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D130" t="s">
         <v>176</v>
       </c>
-      <c r="E128" t="s">
-        <v>7</v>
-      </c>
-      <c r="F128" t="s">
+      <c r="E130" t="s">
+        <v>7</v>
+      </c>
+      <c r="F130" t="s">
         <v>456</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A129" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
         <v>457</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B131" t="s">
         <v>286</v>
       </c>
-      <c r="C129" t="s">
+      <c r="C131" t="s">
         <v>458</v>
       </c>
-      <c r="D129" t="s">
+      <c r="D131" t="s">
         <v>287</v>
       </c>
-      <c r="E129" t="s">
-        <v>7</v>
-      </c>
-      <c r="F129" t="s">
+      <c r="E131" t="s">
+        <v>7</v>
+      </c>
+      <c r="F131" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A130" t="s">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
         <v>460</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B132" t="s">
         <v>461</v>
       </c>
-      <c r="C130" t="s">
+      <c r="C132" t="s">
         <v>462</v>
       </c>
-      <c r="D130" t="s">
+      <c r="D132" t="s">
         <v>462</v>
       </c>
-      <c r="E130" t="s">
-        <v>7</v>
-      </c>
-      <c r="F130" t="s">
+      <c r="E132" t="s">
+        <v>7</v>
+      </c>
+      <c r="F132" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A131" t="s">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
         <v>464</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B133" t="s">
         <v>465</v>
       </c>
-      <c r="C131" t="s">
+      <c r="C133" t="s">
         <v>116</v>
       </c>
-      <c r="D131" t="s">
+      <c r="D133" t="s">
         <v>120</v>
       </c>
-      <c r="E131" t="s">
-        <v>7</v>
-      </c>
-      <c r="F131" t="s">
+      <c r="E133" t="s">
+        <v>7</v>
+      </c>
+      <c r="F133" t="s">
         <v>466</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I131">
-    <sortCondition ref="A120:A131"/>
+  <autoFilter ref="A1:A132" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:I133">
+    <sortCondition ref="A1:A133"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
